--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-10 14:33</t>
+          <t>更新时间: 2026-10-11 14:40</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-11 14:40</t>
+          <t>更新时间: 2026-10-12 14:49</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-12 14:49</t>
+          <t>更新时间: 2026-10-13 15:14</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-13 15:14</t>
+          <t>更新时间: 2026-10-14 13:39</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-14 13:39</t>
+          <t>更新时间: 2026-10-15 13:25</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-15 13:25</t>
+          <t>更新时间: 2026-10-16 13:18</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-16 13:18</t>
+          <t>更新时间: 2026-10-17 13:13</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-17 13:13</t>
+          <t>更新时间: 2026-10-18 13:17</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-18 13:17</t>
+          <t>更新时间: 2026-10-19 13:31</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-19 13:31</t>
+          <t>更新时间: 2026-10-20 13:35</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-20 13:35</t>
+          <t>更新时间: 2026-10-21 13:35</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-21 13:35</t>
+          <t>更新时间: 2026-10-22 13:37</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-22 13:37</t>
+          <t>更新时间: 2026-10-23 13:36</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-23 13:36</t>
+          <t>更新时间: 2026-10-24 13:15</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-24 13:15</t>
+          <t>更新时间: 2026-10-25 13:32</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-25 13:32</t>
+          <t>更新时间: 2026-10-26 13:38</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-26 13:38</t>
+          <t>更新时间: 2026-10-27 13:49</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-27 13:49</t>
+          <t>更新时间: 2026-10-27 15:36</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-27 15:36</t>
+          <t>更新时间: 2026-10-27 15:39</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-27 15:39</t>
+          <t>更新时间: 2026-10-27 15:43</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-27 15:43</t>
+          <t>更新时间: 2026-10-28 09:42</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-28 09:42</t>
+          <t>更新时间: 2026-10-29 09:45</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-29 09:45</t>
+          <t>更新时间: 2026-10-30 09:45</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-30 09:45</t>
+          <t>更新时间: 2026-10-31 09:43</t>
         </is>
       </c>
     </row>
